--- a/data/trans_dic/P56$amigo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,74</t>
+          <t>0,0; 57,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,62</t>
+          <t>0,0; 24,43</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,82</t>
+          <t>0,0; 34,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,32 +882,32 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,73</t>
+          <t>0,0; 33,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,68</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,3</t>
+          <t>0,0; 61,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,57</t>
+          <t>0,0; 40,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,85</t>
+          <t>0,0; 23,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,51</t>
+          <t>1,28; 12,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,25</t>
+          <t>0,0; 59,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 18,8</t>
+          <t>2,14; 20,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 20,49</t>
+          <t>2,72; 20,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,53</t>
+          <t>2,57; 11,78</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,09</t>
+          <t>0,0; 48,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,62</t>
+          <t>0,0; 15,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 10,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,33</t>
+          <t>0,0; 21,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,48; 4,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 19,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 8,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,96</t>
+          <t>0,85; 5,03</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,75</t>
+          <t>0,57; 5,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,65</t>
+          <t>0,58; 5,04</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 16,78</t>
+          <t>2,1; 15,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,4</t>
+          <t>1,55; 8,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,9</t>
+          <t>1,02; 5,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,01</t>
+          <t>0,44; 5,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,01</t>
+          <t>1,61; 4,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,32</t>
+          <t>1,39; 8,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,1</t>
+          <t>0,74; 4,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,74</t>
+          <t>0,41; 3,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,91</t>
+          <t>2,01; 4,95</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2378</t>
+          <t>0; 3364</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1351</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2129</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2846</t>
+          <t>0; 2824</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1483</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3310</t>
+          <t>0; 3003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,32 +2160,32 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1475</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2410</t>
+          <t>0; 2677</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 4066</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1941</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1393</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1649</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1513</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5607</t>
+          <t>0; 6439</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1641</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 6618</t>
+          <t>0; 7205</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1768</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 996</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6435</t>
+          <t>0; 6891</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>615; 6325</t>
+          <t>645; 6309</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4725</t>
+          <t>0; 4362</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2436</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>600; 5300</t>
+          <t>603; 5785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1004; 7544</t>
+          <t>1002; 7570</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2151</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1834; 9078</t>
+          <t>2026; 9271</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4210</t>
+          <t>0; 5013</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1687</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2836</t>
+          <t>0; 2850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7553</t>
+          <t>0; 6691</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6915</t>
+          <t>0; 7763</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3854</t>
+          <t>400; 3875</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4710</t>
+          <t>0; 5274</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7452</t>
+          <t>0; 6757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7570</t>
+          <t>0; 7567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>874; 5010</t>
+          <t>863; 5079</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2085</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5239</t>
+          <t>0; 4737</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5490</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>599; 5934</t>
+          <t>593; 5419</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2085</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5239</t>
+          <t>0; 4737</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5490</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>598; 5958</t>
+          <t>616; 5310</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1008; 8102</t>
+          <t>1013; 7266</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1672; 8317</t>
+          <t>1539; 8887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7043</t>
+          <t>0; 6632</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2105; 12042</t>
+          <t>2089; 12130</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>991; 8538</t>
+          <t>749; 9083</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4066; 12347</t>
+          <t>3963; 11768</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1926; 10378</t>
+          <t>1978; 11567</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2086; 11605</t>
+          <t>2087; 12251</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>979; 9075</t>
+          <t>988; 9340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7057; 16955</t>
+          <t>6952; 17088</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$amigo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Clase-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,64</t>
+          <t>0,0; 46,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,43</t>
+          <t>0,0; 31,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,31</t>
+          <t>0,0; 33,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,02</t>
+          <t>0,0; 26,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,64</t>
+          <t>0,0; 21,18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,21</t>
+          <t>0,0; 53,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,9</t>
+          <t>0,0; 32,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,39</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,48</t>
+          <t>1,07; 12,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,31</t>
+          <t>0,0; 59,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,53</t>
+          <t>2,09; 18,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 20,56</t>
+          <t>2,69; 20,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,78</t>
+          <t>2,53; 12,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,93</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,7</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,44 +1302,44 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,24</t>
+          <t>0,0; 10,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,7</t>
+          <t>0,0; 20,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,68</t>
+          <t>0,44; 4,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,17</t>
+          <t>0,0; 21,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,09</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,32</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,03</t>
+          <t>0,89; 4,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,25</t>
+          <t>0,6; 5,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,04</t>
+          <t>0,57; 5,26</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,05</t>
+          <t>2,1; 15,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,97</t>
+          <t>1,36; 8,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,94</t>
+          <t>1,03; 5,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,32</t>
+          <t>0,18; 5,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,78</t>
+          <t>1,56; 4,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,16</t>
+          <t>1,37; 7,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,33</t>
+          <t>0,74; 3,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,85</t>
+          <t>0,4; 3,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,95</t>
+          <t>1,92; 4,75</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>645</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>645</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>0; 2941</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2824</t>
+          <t>0; 3842</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>603</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1291</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3003</t>
+          <t>0; 3013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2677</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4155</t>
+          <t>0; 3944</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6439</t>
+          <t>0; 5588</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 7205</t>
+          <t>0; 5666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4897</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6891</t>
+          <t>0; 6090</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645; 6309</t>
+          <t>584; 6833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4362</t>
+          <t>0; 4383</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>603; 5785</t>
+          <t>629; 5553</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1002; 7570</t>
+          <t>992; 7524</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026; 9271</t>
+          <t>2141; 10238</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2442</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5013</t>
+          <t>0; 4071</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2850</t>
+          <t>0; 2957</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2784,44 +2784,44 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6691</t>
+          <t>0; 7007</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7763</t>
+          <t>0; 7348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>400; 3875</t>
+          <t>396; 4129</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5274</t>
+          <t>0; 5791</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6757</t>
+          <t>0; 6431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7567</t>
+          <t>0; 7237</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>863; 5079</t>
+          <t>971; 5395</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2608</t>
         </is>
       </c>
     </row>
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4737</t>
+          <t>0; 5411</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6430</t>
+          <t>0; 5817</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>593; 5419</t>
+          <t>672; 5835</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4737</t>
+          <t>0; 5411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6430</t>
+          <t>0; 5817</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>616; 5310</t>
+          <t>650; 6052</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11884</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1013; 7266</t>
+          <t>1012; 7720</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3190,47 +3190,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1539; 8887</t>
+          <t>1423; 8509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6763</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2089; 12130</t>
+          <t>2099; 12128</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>749; 9083</t>
+          <t>304; 8938</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3963; 11768</t>
+          <t>4219; 12584</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1978; 11567</t>
+          <t>1937; 11320</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2087; 12251</t>
+          <t>2098; 11254</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>988; 9340</t>
+          <t>968; 8456</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6952; 17088</t>
+          <t>7205; 17789</t>
         </is>
       </c>
     </row>
